--- a/Excel/CodeConfig.xlsx
+++ b/Excel/CodeConfig.xlsx
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="95">
   <si>
     <t>#</t>
   </si>
@@ -292,6 +292,9 @@
   </si>
   <si>
     <t>gx110</t>
+  </si>
+  <si>
+    <t>bc113</t>
   </si>
   <si>
     <t>tt105</t>
@@ -1993,6 +1996,29 @@
         <v>72</v>
       </c>
     </row>
+    <row r="30" customHeight="1" spans="1:9">
+      <c r="C30" s="1">
+        <v>46</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F30" s="1">
+        <v>5</v>
+      </c>
+      <c r="G30" s="1">
+        <v>5002</v>
+      </c>
+      <c r="H30" s="6">
+        <v>1666</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
     <row r="31" customHeight="1" spans="1:9">
       <c r="A31" s="1" t="s">
         <v>0</v>
@@ -2007,7 +2033,7 @@
         <v>1</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F31" s="11" t="s">
         <v>34</v>
@@ -2169,19 +2195,19 @@
         <v>99</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2192,19 +2218,19 @@
         <v>99</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2215,19 +2241,19 @@
         <v>99</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2238,19 +2264,19 @@
         <v>99</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2261,19 +2287,19 @@
         <v>99</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2284,19 +2310,19 @@
         <v>99</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2317,7 +2343,7 @@
     </row>
     <row r="16" customHeight="1" spans="1:19">
       <c r="G16" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H16" s="4"/>
     </row>
@@ -2468,7 +2494,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>14</v>
@@ -2480,7 +2506,7 @@
         <v>15</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" customFormat="1" ht="18" customHeight="1" spans="1:19">
@@ -2493,7 +2519,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>48</v>
@@ -2502,7 +2528,7 @@
         <v>49</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I7" s="13" t="s">
         <v>51</v>
@@ -2516,7 +2542,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>48</v>
@@ -2525,7 +2551,7 @@
         <v>49</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I8" s="13" t="s">
         <v>51</v>
@@ -2575,7 +2601,7 @@
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="G26" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H26" s="4"/>
     </row>

--- a/Excel/CodeConfig.xlsx
+++ b/Excel/CodeConfig.xlsx
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="99">
   <si>
     <t>#</t>
   </si>
@@ -295,6 +295,18 @@
   </si>
   <si>
     <t>bc113</t>
+  </si>
+  <si>
+    <t>5,5</t>
+  </si>
+  <si>
+    <t>5002,5001</t>
+  </si>
+  <si>
+    <t>1666,166666</t>
+  </si>
+  <si>
+    <t>1666黑铁矿+5000铜矿</t>
   </si>
   <si>
     <t>tt105</t>
@@ -2006,17 +2018,17 @@
       <c r="E30" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F30" s="1">
-        <v>5</v>
-      </c>
-      <c r="G30" s="1">
-        <v>5002</v>
-      </c>
-      <c r="H30" s="6">
-        <v>1666</v>
+      <c r="F30" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="G30" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="H30" s="12" t="s">
+        <v>78</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:9">
@@ -2033,7 +2045,7 @@
         <v>1</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F31" s="11" t="s">
         <v>34</v>
@@ -2195,19 +2207,19 @@
         <v>99</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2218,19 +2230,19 @@
         <v>99</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F7" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="F7" s="11" t="s">
-        <v>78</v>
-      </c>
       <c r="G7" s="11" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2241,19 +2253,19 @@
         <v>99</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="G8" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="F8" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>79</v>
-      </c>
       <c r="H8" s="11" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2264,19 +2276,19 @@
         <v>99</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H9" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2287,19 +2299,19 @@
         <v>99</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2310,19 +2322,19 @@
         <v>99</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2343,7 +2355,7 @@
     </row>
     <row r="16" customHeight="1" spans="1:19">
       <c r="G16" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H16" s="4"/>
     </row>
@@ -2494,7 +2506,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>14</v>
@@ -2506,7 +2518,7 @@
         <v>15</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" customFormat="1" ht="18" customHeight="1" spans="1:19">
@@ -2519,7 +2531,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>48</v>
@@ -2528,7 +2540,7 @@
         <v>49</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="I7" s="13" t="s">
         <v>51</v>
@@ -2542,7 +2554,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>48</v>
@@ -2551,7 +2563,7 @@
         <v>49</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="I8" s="13" t="s">
         <v>51</v>
@@ -2601,7 +2613,7 @@
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="G26" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H26" s="4"/>
     </row>

--- a/Excel/CodeConfig.xlsx
+++ b/Excel/CodeConfig.xlsx
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="103">
   <si>
     <t>#</t>
   </si>
@@ -297,6 +297,18 @@
     <t>bc113</t>
   </si>
   <si>
+    <t>5002</t>
+  </si>
+  <si>
+    <t>1666</t>
+  </si>
+  <si>
+    <t>1666黑铁矿</t>
+  </si>
+  <si>
+    <t>bc115</t>
+  </si>
+  <si>
     <t>5,5</t>
   </si>
   <si>
@@ -306,7 +318,7 @@
     <t>1666,166666</t>
   </si>
   <si>
-    <t>1666黑铁矿+5000铜矿</t>
+    <t>1666黑铁矿+16w铜矿</t>
   </si>
   <si>
     <t>tt105</t>
@@ -1373,7 +1385,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -2019,47 +2031,70 @@
         <v>75</v>
       </c>
       <c r="F30" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="G30" s="11" t="s">
+      <c r="H30" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="H30" s="12" t="s">
+      <c r="I30" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="I30" s="1" t="s">
+    </row>
+    <row r="31" customHeight="1" spans="1:9">
+      <c r="C31" s="1">
+        <v>47</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="31" customHeight="1" spans="1:9">
-      <c r="A31" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C31" s="1">
+      <c r="F31" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="G31" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="H31" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="1:9">
+      <c r="A32" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C32" s="1">
         <v>100</v>
       </c>
-      <c r="D31" s="1">
-        <v>1</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="F31" s="11" t="s">
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="F32" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="G31" s="13" t="s">
+      <c r="G32" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="H31" s="12" t="s">
+      <c r="H32" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="I31" s="9"/>
-    </row>
-    <row r="43" customHeight="1" spans="11:11">
-      <c r="K43" s="10"/>
+      <c r="I32" s="9"/>
+    </row>
+    <row r="44" customHeight="1" spans="11:11">
+      <c r="K44" s="10"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2207,19 +2242,19 @@
         <v>99</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2230,19 +2265,19 @@
         <v>99</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F7" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="F7" s="11" t="s">
-        <v>82</v>
-      </c>
       <c r="G7" s="11" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2253,19 +2288,19 @@
         <v>99</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="G8" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="F8" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>83</v>
-      </c>
       <c r="H8" s="11" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2276,19 +2311,19 @@
         <v>99</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H9" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2299,19 +2334,19 @@
         <v>99</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2322,19 +2357,19 @@
         <v>99</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2355,7 +2390,7 @@
     </row>
     <row r="16" customHeight="1" spans="1:19">
       <c r="G16" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H16" s="4"/>
     </row>
@@ -2506,7 +2541,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>14</v>
@@ -2518,7 +2553,7 @@
         <v>15</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" customFormat="1" ht="18" customHeight="1" spans="1:19">
@@ -2531,7 +2566,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>48</v>
@@ -2540,7 +2575,7 @@
         <v>49</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I7" s="13" t="s">
         <v>51</v>
@@ -2554,7 +2589,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>48</v>
@@ -2563,7 +2598,7 @@
         <v>49</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="I8" s="13" t="s">
         <v>51</v>
@@ -2613,7 +2648,7 @@
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="G26" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H26" s="4"/>
     </row>

--- a/Excel/CodeConfig.xlsx
+++ b/Excel/CodeConfig.xlsx
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="108">
   <si>
     <t>#</t>
   </si>
@@ -319,6 +319,21 @@
   </si>
   <si>
     <t>1666黑铁矿+16w铜矿</t>
+  </si>
+  <si>
+    <t>zq2026</t>
+  </si>
+  <si>
+    <t>5,5,8</t>
+  </si>
+  <si>
+    <t>5002,5001,16</t>
+  </si>
+  <si>
+    <t>2666,266666,20</t>
+  </si>
+  <si>
+    <t>2666黑铁矿+26w铜矿+20个红色珍品材料自选</t>
   </si>
   <si>
     <t>tt105</t>
@@ -1385,7 +1400,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -2067,34 +2082,57 @@
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:9">
-      <c r="A32" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="C32" s="1">
+        <v>48</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="G32" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="H32" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="1:11">
+      <c r="A33" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C33" s="1">
         <v>100</v>
       </c>
-      <c r="D32" s="1">
-        <v>1</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="F32" s="11" t="s">
+      <c r="D33" s="1">
+        <v>1</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="F33" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="G32" s="13" t="s">
+      <c r="G33" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="H32" s="12" t="s">
+      <c r="H33" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="I32" s="9"/>
-    </row>
-    <row r="44" customHeight="1" spans="11:11">
-      <c r="K44" s="10"/>
+      <c r="I33" s="9"/>
+    </row>
+    <row r="45" customHeight="1" spans="1:11">
+      <c r="K45" s="10"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2242,19 +2280,19 @@
         <v>99</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2265,19 +2303,19 @@
         <v>99</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2288,19 +2326,19 @@
         <v>99</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F8" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="F8" s="11" t="s">
-        <v>86</v>
-      </c>
       <c r="G8" s="11" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2311,19 +2349,19 @@
         <v>99</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="G9" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="F9" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>87</v>
-      </c>
       <c r="H9" s="11" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2334,19 +2372,19 @@
         <v>99</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="I10" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2357,19 +2395,19 @@
         <v>99</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2390,7 +2428,7 @@
     </row>
     <row r="16" customHeight="1" spans="1:19">
       <c r="G16" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="H16" s="4"/>
     </row>
@@ -2541,7 +2579,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>14</v>
@@ -2553,7 +2591,7 @@
         <v>15</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" customFormat="1" ht="18" customHeight="1" spans="1:19">
@@ -2566,7 +2604,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>48</v>
@@ -2575,7 +2613,7 @@
         <v>49</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="I7" s="13" t="s">
         <v>51</v>
@@ -2589,7 +2627,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>48</v>
@@ -2598,7 +2636,7 @@
         <v>49</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="I8" s="13" t="s">
         <v>51</v>
@@ -2648,7 +2686,7 @@
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="G26" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="H26" s="4"/>
     </row>

--- a/Excel/CodeConfig.xlsx
+++ b/Excel/CodeConfig.xlsx
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="110">
   <si>
     <t>#</t>
   </si>
@@ -336,7 +336,13 @@
     <t>2666黑铁矿+26w铜矿+20个红色珍品材料自选</t>
   </si>
   <si>
-    <t>tt105</t>
+    <t>tt118</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>201</t>
   </si>
   <si>
     <t>dki309d!34</t>
@@ -1059,7 +1065,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1067,12 +1073,16 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1400,14 +1410,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
     <col min="5" max="5" width="15.875" style="1" customWidth="1"/>
     <col min="6" max="6" width="16.625" style="1" customWidth="1"/>
     <col min="7" max="7" width="31.1666666666667" style="1" customWidth="1"/>
-    <col min="8" max="8" width="25.8833333333333" style="6" customWidth="1"/>
+    <col min="8" max="8" width="25.8833333333333" style="7" customWidth="1"/>
     <col min="9" max="9" width="41.4166666666667" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
@@ -1438,7 +1448,7 @@
       <c r="G3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="8" t="s">
         <v>6</v>
       </c>
       <c r="I3" s="2" t="s">
@@ -1461,7 +1471,7 @@
       <c r="G4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="8" t="s">
         <v>6</v>
       </c>
       <c r="I4" s="2" t="s">
@@ -1484,7 +1494,7 @@
       <c r="G5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="8" t="s">
         <v>12</v>
       </c>
       <c r="I5" s="2" t="s">
@@ -1501,13 +1511,13 @@
       <c r="E6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="13" t="s">
         <v>14</v>
       </c>
       <c r="G6" s="3">
         <v>10001</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="14" t="s">
         <v>15</v>
       </c>
       <c r="I6" s="1" t="s">
@@ -1524,13 +1534,13 @@
       <c r="E7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="13" t="s">
         <v>14</v>
       </c>
       <c r="G7" s="3">
         <v>10002</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="H7" s="14" t="s">
         <v>15</v>
       </c>
       <c r="I7" s="1" t="s">
@@ -1547,13 +1557,13 @@
       <c r="E8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="13" t="s">
         <v>14</v>
       </c>
       <c r="G8" s="3">
         <v>10003</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="14" t="s">
         <v>15</v>
       </c>
       <c r="I8" s="1" t="s">
@@ -1570,13 +1580,13 @@
       <c r="E9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="H9" s="14" t="s">
         <v>24</v>
       </c>
       <c r="I9" s="1" t="s">
@@ -1593,13 +1603,13 @@
       <c r="E10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="H10" s="14" t="s">
         <v>27</v>
       </c>
       <c r="I10" s="1" t="s">
@@ -1616,13 +1626,13 @@
       <c r="E11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="H11" s="14" t="s">
         <v>30</v>
       </c>
       <c r="I11" s="1" t="s">
@@ -1639,13 +1649,13 @@
       <c r="E12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="H12" s="14" t="s">
         <v>24</v>
       </c>
       <c r="I12" s="1" t="s">
@@ -1662,20 +1672,20 @@
       <c r="E13" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="13" t="s">
+      <c r="G13" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="12" t="s">
+      <c r="H13" s="14" t="s">
         <v>36</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="14" customFormat="1" customHeight="1" spans="1:9">
+    <row r="14" s="5" customFormat="1" customHeight="1" spans="1:9">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1683,10 +1693,10 @@
       <c r="E14" s="3"/>
       <c r="F14" s="1"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="6"/>
+      <c r="H14" s="7"/>
       <c r="I14" s="3"/>
     </row>
-    <row r="15" customFormat="1" customHeight="1" spans="1:9">
+    <row r="15" s="5" customFormat="1" customHeight="1" spans="1:9">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1">
@@ -1698,20 +1708,20 @@
       <c r="E15" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="G15" s="11" t="s">
+      <c r="G15" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="H15" s="12" t="s">
+      <c r="H15" s="14" t="s">
         <v>24</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="16" customFormat="1" customHeight="1" spans="1:9">
+    <row r="16" s="5" customFormat="1" customHeight="1" spans="1:9">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1">
@@ -1723,202 +1733,202 @@
       <c r="E16" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="H16" s="12" t="s">
+      <c r="H16" s="14" t="s">
         <v>24</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" customFormat="1" customHeight="1" spans="1:9">
+    <row r="17" s="5" customFormat="1" customHeight="1" spans="1:9">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
-      <c r="C17">
+      <c r="C17" s="5">
         <v>12</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="5">
         <v>1</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="G17" s="11" t="s">
+      <c r="G17" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="H17" s="12" t="s">
+      <c r="H17" s="14" t="s">
         <v>41</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="18" customFormat="1" customHeight="1" spans="1:9">
+    <row r="18" s="5" customFormat="1" customHeight="1" spans="1:9">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
-      <c r="C18">
+      <c r="C18" s="5">
         <v>13</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="5">
         <v>1</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="F18" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="G18" s="13" t="s">
+      <c r="G18" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="H18" s="12" t="s">
+      <c r="H18" s="14" t="s">
         <v>45</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="19" customFormat="1" customHeight="1" spans="1:9">
+    <row r="19" s="5" customFormat="1" customHeight="1" spans="1:9">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
-      <c r="C19">
+      <c r="C19" s="5">
         <v>14</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="5">
         <v>1</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="F19" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="G19" s="11" t="s">
+      <c r="G19" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="H19" s="12" t="s">
+      <c r="H19" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="I19" s="13" t="s">
+      <c r="I19" s="15" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="20" customFormat="1" customHeight="1" spans="1:9">
+    <row r="20" s="5" customFormat="1" customHeight="1" spans="1:9">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
-      <c r="C20">
+      <c r="C20" s="5">
         <v>15</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="5">
         <v>1</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="F20" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="G20" s="13" t="s">
+      <c r="G20" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="H20" s="12" t="s">
+      <c r="H20" s="14" t="s">
         <v>45</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="21" customFormat="1" customHeight="1" spans="1:9">
+    <row r="21" s="5" customFormat="1" customHeight="1" spans="1:9">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
-      <c r="C21">
+      <c r="C21" s="5">
         <v>16</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="5">
         <v>1</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="F21" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="G21" s="11" t="s">
+      <c r="G21" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="H21" s="12" t="s">
+      <c r="H21" s="14" t="s">
         <v>41</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="22" customFormat="1" customHeight="1" spans="1:9">
+    <row r="22" s="5" customFormat="1" customHeight="1" spans="1:9">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
-      <c r="C22">
+      <c r="C22" s="5">
         <v>17</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="5">
         <v>1</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="F22" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="G22" s="11" t="s">
+      <c r="G22" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="H22" s="12" t="s">
+      <c r="H22" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="I22" s="13" t="s">
+      <c r="I22" s="15" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="23" customFormat="1" customHeight="1" spans="1:9">
+    <row r="23" s="5" customFormat="1" customHeight="1" spans="1:9">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
-      <c r="C23">
+      <c r="C23" s="5">
         <v>18</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="5">
         <v>1</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="F23" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="G23" s="13" t="s">
+      <c r="G23" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="H23" s="12" t="s">
+      <c r="H23" s="14" t="s">
         <v>59</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="24" s="5" customFormat="1" customHeight="1" spans="1:9">
-      <c r="A24" s="5" t="s">
+    <row r="24" s="6" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A24" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="H24" s="8"/>
+      <c r="H24" s="9"/>
     </row>
     <row r="25" customHeight="1" spans="1:9">
       <c r="C25" s="1">
@@ -1930,13 +1940,13 @@
       <c r="E25" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="F25" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="G25" s="11" t="s">
+      <c r="G25" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="H25" s="12" t="s">
+      <c r="H25" s="14" t="s">
         <v>65</v>
       </c>
       <c r="I25" s="1" t="s">
@@ -1953,13 +1963,13 @@
       <c r="E26" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F26" s="11" t="s">
+      <c r="F26" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="G26" s="11" t="s">
+      <c r="G26" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="H26" s="12" t="s">
+      <c r="H26" s="14" t="s">
         <v>69</v>
       </c>
       <c r="I26" s="1" t="s">
@@ -1982,7 +1992,7 @@
       <c r="G27" s="1">
         <v>5002</v>
       </c>
-      <c r="H27" s="6">
+      <c r="H27" s="7">
         <v>666</v>
       </c>
       <c r="I27" s="1" t="s">
@@ -2005,7 +2015,7 @@
       <c r="G28" s="1">
         <v>5002</v>
       </c>
-      <c r="H28" s="6">
+      <c r="H28" s="7">
         <v>666</v>
       </c>
       <c r="I28" s="1" t="s">
@@ -2028,7 +2038,7 @@
       <c r="G29" s="1">
         <v>5002</v>
       </c>
-      <c r="H29" s="6">
+      <c r="H29" s="7">
         <v>2666</v>
       </c>
       <c r="I29" s="1" t="s">
@@ -2045,13 +2055,13 @@
       <c r="E30" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F30" s="11" t="s">
+      <c r="F30" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="G30" s="11" t="s">
+      <c r="G30" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="H30" s="12" t="s">
+      <c r="H30" s="14" t="s">
         <v>77</v>
       </c>
       <c r="I30" s="1" t="s">
@@ -2068,13 +2078,13 @@
       <c r="E31" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F31" s="11" t="s">
+      <c r="F31" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="G31" s="11" t="s">
+      <c r="G31" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="H31" s="12" t="s">
+      <c r="H31" s="14" t="s">
         <v>82</v>
       </c>
       <c r="I31" s="1" t="s">
@@ -2091,48 +2101,42 @@
       <c r="E32" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F32" s="11" t="s">
+      <c r="F32" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="G32" s="11" t="s">
+      <c r="G32" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="H32" s="12" t="s">
+      <c r="H32" s="14" t="s">
         <v>87</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="33" customHeight="1" spans="1:11">
-      <c r="A33" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C33" s="1">
+    <row r="43" customHeight="1" spans="3:9">
+      <c r="C43" s="1">
         <v>100</v>
       </c>
-      <c r="D33" s="1">
-        <v>1</v>
-      </c>
-      <c r="E33" s="9" t="s">
+      <c r="D43" s="1">
+        <v>1</v>
+      </c>
+      <c r="E43" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="F33" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="G33" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="H33" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="I33" s="9"/>
-    </row>
-    <row r="45" customHeight="1" spans="1:11">
-      <c r="K45" s="10"/>
+      <c r="F43" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="G43" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="H43" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I43" s="11"/>
+    </row>
+    <row r="55" customHeight="1" spans="11:11">
+      <c r="K55" s="12"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2280,19 +2284,19 @@
         <v>99</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="G6" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="F6" s="13" t="s">
         <v>93</v>
       </c>
+      <c r="G6" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>95</v>
+      </c>
       <c r="I6" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2303,19 +2307,19 @@
         <v>99</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="H7" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="F7" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>93</v>
-      </c>
       <c r="I7" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2326,19 +2330,19 @@
         <v>99</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2349,19 +2353,19 @@
         <v>99</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>100</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2372,19 +2376,19 @@
         <v>99</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="H10" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="F10" s="13" t="s">
         <v>93</v>
       </c>
+      <c r="G10" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>95</v>
+      </c>
       <c r="I10" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2395,19 +2399,19 @@
         <v>99</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="H11" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="F11" s="13" t="s">
         <v>93</v>
       </c>
+      <c r="G11" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>95</v>
+      </c>
       <c r="I11" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2428,7 +2432,7 @@
     </row>
     <row r="16" customHeight="1" spans="1:19">
       <c r="G16" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H16" s="4"/>
     </row>
@@ -2579,19 +2583,19 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="F6" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="F6" s="13" t="s">
         <v>14</v>
       </c>
       <c r="G6" s="3">
         <v>10004</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="16" t="s">
         <v>15</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" customFormat="1" ht="18" customHeight="1" spans="1:19">
@@ -2604,18 +2608,18 @@
         <v>1</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="F7" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="F7" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="H7" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="I7" s="13" t="s">
+      <c r="H7" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="I7" s="15" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2627,18 +2631,18 @@
         <v>1</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="F8" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="F8" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="H8" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="I8" s="13" t="s">
+      <c r="H8" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="I8" s="15" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2686,7 +2690,7 @@
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="G26" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H26" s="4"/>
     </row>

--- a/Excel/CodeConfig.xlsx
+++ b/Excel/CodeConfig.xlsx
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="129">
   <si>
     <t>#</t>
   </si>
@@ -336,6 +336,9 @@
     <t>2666黑铁矿+26w铜矿+20个红色珍品材料自选</t>
   </si>
   <si>
+    <t>1012026</t>
+  </si>
+  <si>
     <t>tt118</t>
   </si>
   <si>
@@ -397,6 +400,60 @@
   </si>
   <si>
     <t>200,160,120,80,40</t>
+  </si>
+  <si>
+    <t>cw1</t>
+  </si>
+  <si>
+    <t>宠物1</t>
+  </si>
+  <si>
+    <t>cw2</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>宠物2</t>
+  </si>
+  <si>
+    <t>cw3</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>宠物3</t>
+  </si>
+  <si>
+    <t>cw4</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>宠物4</t>
+  </si>
+  <si>
+    <t>cw5</t>
+  </si>
+  <si>
+    <t>宠物5</t>
+  </si>
+  <si>
+    <t>cw6</t>
+  </si>
+  <si>
+    <t>cw7</t>
+  </si>
+  <si>
+    <t>cw8</t>
+  </si>
+  <si>
+    <t>cw9</t>
+  </si>
+  <si>
+    <t>cw10</t>
   </si>
 </sst>
 </file>
@@ -1065,7 +1122,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1073,7 +1130,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1417,7 +1473,7 @@
     <col min="5" max="5" width="15.875" style="1" customWidth="1"/>
     <col min="6" max="6" width="16.625" style="1" customWidth="1"/>
     <col min="7" max="7" width="31.1666666666667" style="1" customWidth="1"/>
-    <col min="8" max="8" width="25.8833333333333" style="7" customWidth="1"/>
+    <col min="8" max="8" width="25.8833333333333" style="6" customWidth="1"/>
     <col min="9" max="9" width="41.4166666666667" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
@@ -1448,7 +1504,7 @@
       <c r="G3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="7" t="s">
         <v>6</v>
       </c>
       <c r="I3" s="2" t="s">
@@ -1471,7 +1527,7 @@
       <c r="G4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="7" t="s">
         <v>6</v>
       </c>
       <c r="I4" s="2" t="s">
@@ -1494,7 +1550,7 @@
       <c r="G5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="7" t="s">
         <v>12</v>
       </c>
       <c r="I5" s="2" t="s">
@@ -1511,13 +1567,13 @@
       <c r="E6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="12" t="s">
         <v>14</v>
       </c>
       <c r="G6" s="3">
         <v>10001</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="13" t="s">
         <v>15</v>
       </c>
       <c r="I6" s="1" t="s">
@@ -1534,13 +1590,13 @@
       <c r="E7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="12" t="s">
         <v>14</v>
       </c>
       <c r="G7" s="3">
         <v>10002</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="H7" s="13" t="s">
         <v>15</v>
       </c>
       <c r="I7" s="1" t="s">
@@ -1557,13 +1613,13 @@
       <c r="E8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="12" t="s">
         <v>14</v>
       </c>
       <c r="G8" s="3">
         <v>10003</v>
       </c>
-      <c r="H8" s="14" t="s">
+      <c r="H8" s="13" t="s">
         <v>15</v>
       </c>
       <c r="I8" s="1" t="s">
@@ -1580,13 +1636,13 @@
       <c r="E9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="G9" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="H9" s="14" t="s">
+      <c r="H9" s="13" t="s">
         <v>24</v>
       </c>
       <c r="I9" s="1" t="s">
@@ -1603,13 +1659,13 @@
       <c r="E10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="F10" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="G10" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="14" t="s">
+      <c r="H10" s="13" t="s">
         <v>27</v>
       </c>
       <c r="I10" s="1" t="s">
@@ -1626,13 +1682,13 @@
       <c r="E11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="13" t="s">
+      <c r="G11" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="H11" s="14" t="s">
+      <c r="H11" s="13" t="s">
         <v>30</v>
       </c>
       <c r="I11" s="1" t="s">
@@ -1649,13 +1705,13 @@
       <c r="E12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="H12" s="14" t="s">
+      <c r="H12" s="13" t="s">
         <v>24</v>
       </c>
       <c r="I12" s="1" t="s">
@@ -1672,20 +1728,20 @@
       <c r="E13" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="F13" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="15" t="s">
+      <c r="G13" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="14" t="s">
+      <c r="H13" s="13" t="s">
         <v>36</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="14" s="5" customFormat="1" customHeight="1" spans="1:9">
+    <row r="14" s="3" customFormat="1" customHeight="1" spans="1:9">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1693,10 +1749,9 @@
       <c r="E14" s="3"/>
       <c r="F14" s="1"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="3"/>
-    </row>
-    <row r="15" s="5" customFormat="1" customHeight="1" spans="1:9">
+      <c r="H14" s="6"/>
+    </row>
+    <row r="15" s="3" customFormat="1" customHeight="1" spans="1:9">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1">
@@ -1708,20 +1763,20 @@
       <c r="E15" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="F15" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G15" s="13" t="s">
+      <c r="G15" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="H15" s="14" t="s">
+      <c r="H15" s="13" t="s">
         <v>24</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="16" s="5" customFormat="1" customHeight="1" spans="1:9">
+    <row r="16" s="3" customFormat="1" customHeight="1" spans="1:9">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1">
@@ -1733,202 +1788,202 @@
       <c r="E16" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="13" t="s">
+      <c r="F16" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G16" s="13" t="s">
+      <c r="G16" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="H16" s="14" t="s">
+      <c r="H16" s="13" t="s">
         <v>24</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" s="5" customFormat="1" customHeight="1" spans="1:9">
+    <row r="17" s="3" customFormat="1" customHeight="1" spans="1:9">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
-      <c r="C17" s="5">
+      <c r="C17" s="3">
         <v>12</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="3">
         <v>1</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F17" s="13" t="s">
+      <c r="F17" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G17" s="13" t="s">
+      <c r="G17" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="H17" s="14" t="s">
+      <c r="H17" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="18" s="5" customFormat="1" customHeight="1" spans="1:9">
+    <row r="18" s="3" customFormat="1" customHeight="1" spans="1:9">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
-      <c r="C18" s="5">
+      <c r="C18" s="3">
         <v>13</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="3">
         <v>1</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F18" s="13" t="s">
+      <c r="F18" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="G18" s="15" t="s">
+      <c r="G18" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="H18" s="14" t="s">
+      <c r="H18" s="13" t="s">
         <v>45</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="19" s="5" customFormat="1" customHeight="1" spans="1:9">
+    <row r="19" s="3" customFormat="1" customHeight="1" spans="1:9">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
-      <c r="C19" s="5">
+      <c r="C19" s="3">
         <v>14</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D19" s="3">
         <v>1</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F19" s="13" t="s">
+      <c r="F19" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="G19" s="13" t="s">
+      <c r="G19" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="H19" s="14" t="s">
+      <c r="H19" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="I19" s="15" t="s">
+      <c r="I19" s="14" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="20" s="5" customFormat="1" customHeight="1" spans="1:9">
+    <row r="20" s="3" customFormat="1" customHeight="1" spans="1:9">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
-      <c r="C20" s="5">
+      <c r="C20" s="3">
         <v>15</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20" s="3">
         <v>1</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="F20" s="13" t="s">
+      <c r="F20" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="G20" s="15" t="s">
+      <c r="G20" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="H20" s="14" t="s">
+      <c r="H20" s="13" t="s">
         <v>45</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="21" s="5" customFormat="1" customHeight="1" spans="1:9">
+    <row r="21" s="3" customFormat="1" customHeight="1" spans="1:9">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
-      <c r="C21" s="5">
+      <c r="C21" s="3">
         <v>16</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D21" s="3">
         <v>1</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F21" s="13" t="s">
+      <c r="F21" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G21" s="13" t="s">
+      <c r="G21" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="H21" s="14" t="s">
+      <c r="H21" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="22" s="5" customFormat="1" customHeight="1" spans="1:9">
+    <row r="22" s="3" customFormat="1" customHeight="1" spans="1:9">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
-      <c r="C22" s="5">
+      <c r="C22" s="3">
         <v>17</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="3">
         <v>1</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F22" s="13" t="s">
+      <c r="F22" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="G22" s="13" t="s">
+      <c r="G22" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="H22" s="14" t="s">
+      <c r="H22" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="I22" s="15" t="s">
+      <c r="I22" s="14" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="23" s="5" customFormat="1" customHeight="1" spans="1:9">
+    <row r="23" s="3" customFormat="1" customHeight="1" spans="1:9">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
-      <c r="C23" s="5">
+      <c r="C23" s="3">
         <v>18</v>
       </c>
-      <c r="D23" s="5">
+      <c r="D23" s="3">
         <v>1</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F23" s="13" t="s">
+      <c r="F23" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="G23" s="15" t="s">
+      <c r="G23" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="H23" s="14" t="s">
+      <c r="H23" s="13" t="s">
         <v>59</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="24" s="6" customFormat="1" customHeight="1" spans="1:9">
-      <c r="A24" s="6" t="s">
+    <row r="24" s="5" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A24" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="H24" s="9"/>
+      <c r="H24" s="8"/>
     </row>
     <row r="25" customHeight="1" spans="1:9">
       <c r="C25" s="1">
@@ -1940,13 +1995,13 @@
       <c r="E25" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F25" s="13" t="s">
+      <c r="F25" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="G25" s="13" t="s">
+      <c r="G25" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="H25" s="14" t="s">
+      <c r="H25" s="13" t="s">
         <v>65</v>
       </c>
       <c r="I25" s="1" t="s">
@@ -1963,13 +2018,13 @@
       <c r="E26" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F26" s="13" t="s">
+      <c r="F26" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="G26" s="13" t="s">
+      <c r="G26" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="H26" s="14" t="s">
+      <c r="H26" s="13" t="s">
         <v>69</v>
       </c>
       <c r="I26" s="1" t="s">
@@ -1992,7 +2047,7 @@
       <c r="G27" s="1">
         <v>5002</v>
       </c>
-      <c r="H27" s="7">
+      <c r="H27" s="6">
         <v>666</v>
       </c>
       <c r="I27" s="1" t="s">
@@ -2015,7 +2070,7 @@
       <c r="G28" s="1">
         <v>5002</v>
       </c>
-      <c r="H28" s="7">
+      <c r="H28" s="6">
         <v>666</v>
       </c>
       <c r="I28" s="1" t="s">
@@ -2038,7 +2093,7 @@
       <c r="G29" s="1">
         <v>5002</v>
       </c>
-      <c r="H29" s="7">
+      <c r="H29" s="6">
         <v>2666</v>
       </c>
       <c r="I29" s="1" t="s">
@@ -2055,13 +2110,13 @@
       <c r="E30" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F30" s="13" t="s">
+      <c r="F30" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="G30" s="13" t="s">
+      <c r="G30" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="H30" s="14" t="s">
+      <c r="H30" s="13" t="s">
         <v>77</v>
       </c>
       <c r="I30" s="1" t="s">
@@ -2078,13 +2133,13 @@
       <c r="E31" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F31" s="13" t="s">
+      <c r="F31" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="G31" s="13" t="s">
+      <c r="G31" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="H31" s="14" t="s">
+      <c r="H31" s="13" t="s">
         <v>82</v>
       </c>
       <c r="I31" s="1" t="s">
@@ -2101,42 +2156,71 @@
       <c r="E32" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F32" s="13" t="s">
+      <c r="F32" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="G32" s="13" t="s">
+      <c r="G32" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="H32" s="14" t="s">
+      <c r="H32" s="13" t="s">
         <v>87</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="43" customHeight="1" spans="3:9">
+    <row r="33" customHeight="1" spans="1:9">
+      <c r="C33" s="1">
+        <v>49</v>
+      </c>
+      <c r="D33" s="1">
+        <v>1</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="G33" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="1:9">
+      <c r="A43" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C43" s="1">
         <v>100</v>
       </c>
       <c r="D43" s="1">
         <v>1</v>
       </c>
-      <c r="E43" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="F43" s="13" t="s">
+      <c r="E43" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="G43" s="15" t="s">
+      <c r="F43" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="H43" s="14" t="s">
+      <c r="G43" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="H43" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="I43" s="11"/>
+      <c r="I43" s="10"/>
     </row>
     <row r="55" customHeight="1" spans="11:11">
-      <c r="K55" s="12"/>
+      <c r="K55" s="11"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2284,19 +2368,19 @@
         <v>99</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F6" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="F6" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="H6" s="13" t="s">
+      <c r="G6" s="12" t="s">
         <v>95</v>
       </c>
+      <c r="H6" s="12" t="s">
+        <v>96</v>
+      </c>
       <c r="I6" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2307,19 +2391,19 @@
         <v>99</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2330,19 +2414,19 @@
         <v>99</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="G8" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="F8" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="H8" s="13" t="s">
+      <c r="G8" s="12" t="s">
         <v>95</v>
       </c>
+      <c r="H8" s="12" t="s">
+        <v>96</v>
+      </c>
       <c r="I8" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2353,19 +2437,19 @@
         <v>99</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="G9" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="F9" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="H9" s="13" t="s">
-        <v>100</v>
+      <c r="G9" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>101</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2376,19 +2460,19 @@
         <v>99</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="G10" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="F10" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="H10" s="13" t="s">
+      <c r="G10" s="12" t="s">
         <v>95</v>
       </c>
+      <c r="H10" s="12" t="s">
+        <v>96</v>
+      </c>
       <c r="I10" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2399,19 +2483,19 @@
         <v>99</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="G11" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="F11" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="H11" s="13" t="s">
+      <c r="G11" s="12" t="s">
         <v>95</v>
       </c>
+      <c r="H11" s="12" t="s">
+        <v>96</v>
+      </c>
       <c r="I11" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2432,7 +2516,7 @@
     </row>
     <row r="16" customHeight="1" spans="1:19">
       <c r="G16" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H16" s="4"/>
     </row>
@@ -2583,19 +2667,19 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="F6" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="F6" s="12" t="s">
         <v>14</v>
       </c>
       <c r="G6" s="3">
         <v>10004</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="H6" s="15" t="s">
         <v>15</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" customFormat="1" ht="18" customHeight="1" spans="1:19">
@@ -2608,18 +2692,18 @@
         <v>1</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="F7" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="F7" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G7" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="H7" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="I7" s="15" t="s">
+      <c r="H7" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="I7" s="14" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2631,18 +2715,18 @@
         <v>1</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="F8" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="F8" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="G8" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="H8" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="I8" s="15" t="s">
+      <c r="H8" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="I8" s="14" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2650,37 +2734,241 @@
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
     </row>
-    <row r="15" customFormat="1" customHeight="1"/>
-    <row r="16" customFormat="1" customHeight="1"/>
-    <row r="17" customFormat="1" customHeight="1"/>
-    <row r="18" customFormat="1" customHeight="1"/>
-    <row r="19" customFormat="1" customHeight="1"/>
+    <row r="14" customHeight="1" spans="1:19">
+      <c r="C14" s="1">
+        <v>40011</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" customHeight="1" spans="1:19">
+      <c r="C15" s="1">
+        <v>40012</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" customHeight="1" spans="1:19">
+      <c r="C16" s="1">
+        <v>40013</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="17" customFormat="1" customHeight="1" spans="1:10">
+      <c r="C17" s="1">
+        <v>40014</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="18" customFormat="1" customHeight="1" spans="1:10">
+      <c r="C18" s="1">
+        <v>40015</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" customHeight="1" spans="1:10">
+      <c r="C19" s="1">
+        <v>40016</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
     <row r="20" customFormat="1" customHeight="1" spans="1:10">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="1"/>
+      <c r="C20" s="1">
+        <v>40017</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>112</v>
+      </c>
       <c r="J20" s="1"/>
     </row>
     <row r="21" customFormat="1" customHeight="1" spans="1:10">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="1"/>
+      <c r="C21" s="1">
+        <v>40018</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>112</v>
+      </c>
       <c r="J21" s="1"/>
     </row>
+    <row r="22" customHeight="1" spans="1:10">
+      <c r="C22" s="1">
+        <v>40019</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="H22" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="H23" s="4"/>
+      <c r="C23" s="1">
+        <v>40020</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="H23" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="H24" s="4"/>
@@ -2690,7 +2978,7 @@
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="G26" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H26" s="4"/>
     </row>
